--- a/make_interface/Chignik Robust Regression.xlsx
+++ b/make_interface/Chignik Robust Regression.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-3.71°</t>
+          <t>-1.13°</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-6.42°</t>
+          <t>-4.52°</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-9.08°</t>
+          <t>-7.87°</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-11.68°</t>
+          <t>-11.14°</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.22°</t>
+          <t>-14.30°</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-16.67°</t>
+          <t>-17.33°</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-19.03°</t>
+          <t>-20.22°</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-21.29°</t>
+          <t>-22.96°</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-23.46°</t>
+          <t>-25.54°</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-25.52°</t>
+          <t>-27.97°</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-27.48°</t>
+          <t>-30.24°</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-29.35°</t>
+          <t>-32.37°</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-30.76°</t>
+          <t>-34.09°</t>
         </is>
       </c>
     </row>
